--- a/samples/corpus/full/chantiers/nacrines/4-reception/liste-des-reserves/2026-04-14_liste-des-reserves-etat-de-levee.xlsx
+++ b/samples/corpus/full/chantiers/nacrines/4-reception/liste-des-reserves/2026-04-14_liste-des-reserves-etat-de-levee.xlsx
@@ -509,7 +509,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Lot 2</t>
+          <t>Lot 3</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
